--- a/gu_in/Item.edf/25_GuardTowerItem/GuardTowerItem.xlsx
+++ b/gu_in/Item.edf/25_GuardTowerItem/GuardTowerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F059AE00-CA93-4948-9D74-D609B62E791B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D54D6-AE0C-4B9D-B6AC-EDF79086EA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GuardTowerItem" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1072,7 +1070,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1087,6 +1085,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1123,12 +1127,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1147,9 +1154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1187,9 +1194,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1222,9 +1229,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1257,9 +1281,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2425,377 +2466,377 @@
       </c>
       <c r="BJ5" s="2"/>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="5">
         <v>40</v>
       </c>
-      <c r="G6" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
+      <c r="G6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
         <v>10</v>
       </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
         <v>40</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="5">
         <v>30</v>
       </c>
-      <c r="N6" s="3">
-        <v>20</v>
-      </c>
-      <c r="O6" s="2">
+      <c r="N6" s="5">
+        <v>20</v>
+      </c>
+      <c r="O6" s="6">
         <v>0.5</v>
       </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
+      <c r="P6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
         <v>330</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="5">
         <v>2000</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="6">
         <v>200</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="5">
         <v>10622</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="5">
         <v>11802</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6" s="6">
         <v>30</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6" s="6">
         <v>50</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6" s="6">
         <v>99</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="5">
         <v>1503</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="6">
         <v>0.5</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6" s="6">
         <v>0.16680499911308289</v>
       </c>
-      <c r="AB6" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>20</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>20</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>20</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="3">
+      <c r="AB6" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>20</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE6" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF6" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="5">
         <v>22570</v>
       </c>
-      <c r="AM6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3">
+      <c r="AM6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="5">
+        <v>1363637</v>
+      </c>
+      <c r="AO6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="5">
+        <v>2500</v>
+      </c>
+      <c r="AT6" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AU6" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AW6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AY6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC6" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="BG6" s="5">
+        <v>11</v>
+      </c>
+      <c r="BH6" s="5">
+        <v>2</v>
+      </c>
+      <c r="BI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="6"/>
+    </row>
+    <row r="7" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="5">
+        <v>45</v>
+      </c>
+      <c r="G7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>10</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>45</v>
+      </c>
+      <c r="M7" s="5">
+        <v>30</v>
+      </c>
+      <c r="N7" s="5">
+        <v>20</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="P7" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>330</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1500</v>
+      </c>
+      <c r="S7" s="6">
+        <v>250</v>
+      </c>
+      <c r="T7" s="5">
+        <v>26655</v>
+      </c>
+      <c r="U7" s="5">
+        <v>29616</v>
+      </c>
+      <c r="V7" s="6">
+        <v>30</v>
+      </c>
+      <c r="W7" s="6">
+        <v>50</v>
+      </c>
+      <c r="X7" s="6">
+        <v>99</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>3110</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>0.11476700007915497</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>20</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF7" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="5">
+        <v>26210</v>
+      </c>
+      <c r="AM7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="5">
+        <v>2272728</v>
+      </c>
+      <c r="AO7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="5">
         <v>50000</v>
       </c>
-      <c r="AO6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AT6" s="3" t="s">
+      <c r="AT7" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="AU6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV6" s="3" t="s">
+      <c r="AU7" s="5">
+        <v>2</v>
+      </c>
+      <c r="AV7" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AW6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX6" s="3" t="s">
+      <c r="AW7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AY6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA6" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB6" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC6" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE6" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="BG6" s="3">
+      <c r="AY7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="BG7" s="5">
         <v>11</v>
       </c>
-      <c r="BH6" s="3">
+      <c r="BH7" s="5">
         <v>2</v>
       </c>
-      <c r="BI6" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ6" s="2"/>
-    </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F7" s="3">
-        <v>45</v>
-      </c>
-      <c r="G7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>10</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3">
-        <v>45</v>
-      </c>
-      <c r="M7" s="3">
-        <v>30</v>
-      </c>
-      <c r="N7" s="3">
-        <v>20</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="P7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>330</v>
-      </c>
-      <c r="R7" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S7" s="2">
-        <v>250</v>
-      </c>
-      <c r="T7" s="3">
-        <v>26655</v>
-      </c>
-      <c r="U7" s="3">
-        <v>29616</v>
-      </c>
-      <c r="V7" s="2">
-        <v>30</v>
-      </c>
-      <c r="W7" s="2">
-        <v>50</v>
-      </c>
-      <c r="X7" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>3110</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>0.11476700007915497</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>20</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>20</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>20</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="3">
-        <v>26210</v>
-      </c>
-      <c r="AM7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="AO7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="3">
-        <v>50000</v>
-      </c>
-      <c r="AT7" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="AU7" s="3">
-        <v>2</v>
-      </c>
-      <c r="AV7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="AW7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="AY7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE7" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG7" s="3">
-        <v>11</v>
-      </c>
-      <c r="BH7" s="3">
-        <v>2</v>
-      </c>
-      <c r="BI7" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ7" s="2"/>
+      <c r="BI7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="6"/>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -6331,377 +6372,377 @@
       </c>
       <c r="BJ26" s="2"/>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="5">
         <v>40</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="G27" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
         <v>10</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5">
         <v>4</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="5">
         <v>40</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="5">
         <v>30</v>
       </c>
-      <c r="N27" s="3">
-        <v>20</v>
-      </c>
-      <c r="O27" s="2">
+      <c r="N27" s="5">
+        <v>20</v>
+      </c>
+      <c r="O27" s="6">
         <v>0.5</v>
       </c>
-      <c r="P27" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="P27" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="5">
         <v>330</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="5">
         <v>2000</v>
       </c>
-      <c r="S27" s="2">
+      <c r="S27" s="6">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="T27" s="5">
         <v>10622</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="5">
         <v>11802</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" s="6">
         <v>30</v>
       </c>
-      <c r="W27" s="2">
+      <c r="W27" s="6">
         <v>50</v>
       </c>
-      <c r="X27" s="2">
+      <c r="X27" s="6">
         <v>99</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="5">
         <v>1503</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="Z27" s="6">
         <v>0.5</v>
       </c>
-      <c r="AA27" s="2">
+      <c r="AA27" s="6">
         <v>0.16680499911308289</v>
       </c>
-      <c r="AB27" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>20</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>20</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>20</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AB27" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AC27" s="5">
+        <v>20</v>
+      </c>
+      <c r="AD27" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE27" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF27" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="5">
         <v>22570</v>
       </c>
-      <c r="AM27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="3">
+      <c r="AM27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="5">
+        <v>1363637</v>
+      </c>
+      <c r="AO27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS27" s="5">
+        <v>2500</v>
+      </c>
+      <c r="AT27" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AU27" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV27" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AW27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX27" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AY27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA27" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB27" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC27" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE27" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG27" s="5">
+        <v>13</v>
+      </c>
+      <c r="BH27" s="5">
+        <v>2</v>
+      </c>
+      <c r="BI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="6"/>
+    </row>
+    <row r="28" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F28" s="5">
+        <v>45</v>
+      </c>
+      <c r="G28" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <v>10</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5">
+        <v>4</v>
+      </c>
+      <c r="L28" s="5">
+        <v>45</v>
+      </c>
+      <c r="M28" s="5">
+        <v>30</v>
+      </c>
+      <c r="N28" s="5">
+        <v>20</v>
+      </c>
+      <c r="O28" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="P28" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>330</v>
+      </c>
+      <c r="R28" s="5">
+        <v>1500</v>
+      </c>
+      <c r="S28" s="6">
+        <v>250</v>
+      </c>
+      <c r="T28" s="5">
+        <v>26655</v>
+      </c>
+      <c r="U28" s="5">
+        <v>29616</v>
+      </c>
+      <c r="V28" s="6">
+        <v>30</v>
+      </c>
+      <c r="W28" s="6">
+        <v>50</v>
+      </c>
+      <c r="X28" s="6">
+        <v>99</v>
+      </c>
+      <c r="Y28" s="5">
+        <v>3110</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA28" s="6">
+        <v>0.11476700007915497</v>
+      </c>
+      <c r="AB28" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AC28" s="5">
+        <v>20</v>
+      </c>
+      <c r="AD28" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE28" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF28" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="5">
+        <v>26210</v>
+      </c>
+      <c r="AM28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="5">
+        <v>2272728</v>
+      </c>
+      <c r="AO28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS28" s="5">
         <v>50000</v>
       </c>
-      <c r="AO27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS27" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AT27" s="3" t="s">
+      <c r="AT28" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="AU27" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV27" s="3" t="s">
+      <c r="AU28" s="5">
+        <v>2</v>
+      </c>
+      <c r="AV28" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AW27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX27" s="3" t="s">
+      <c r="AW28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX28" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AY27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ27" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA27" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB27" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC27" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD27" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE27" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BG27" s="3">
+      <c r="AY28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ28" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA28" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB28" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC28" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD28" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE28" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF28" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BG28" s="5">
         <v>13</v>
       </c>
-      <c r="BH27" s="3">
+      <c r="BH28" s="5">
         <v>2</v>
       </c>
-      <c r="BI27" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ27" s="2"/>
-    </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F28" s="3">
-        <v>45</v>
-      </c>
-      <c r="G28" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>10</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>4</v>
-      </c>
-      <c r="L28" s="3">
-        <v>45</v>
-      </c>
-      <c r="M28" s="3">
-        <v>30</v>
-      </c>
-      <c r="N28" s="3">
-        <v>20</v>
-      </c>
-      <c r="O28" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="P28" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>330</v>
-      </c>
-      <c r="R28" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S28" s="2">
-        <v>250</v>
-      </c>
-      <c r="T28" s="3">
-        <v>26655</v>
-      </c>
-      <c r="U28" s="3">
-        <v>29616</v>
-      </c>
-      <c r="V28" s="2">
-        <v>30</v>
-      </c>
-      <c r="W28" s="2">
-        <v>50</v>
-      </c>
-      <c r="X28" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y28" s="3">
-        <v>3110</v>
-      </c>
-      <c r="Z28" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AA28" s="2">
-        <v>0.11476700007915497</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AC28" s="3">
-        <v>20</v>
-      </c>
-      <c r="AD28" s="3">
-        <v>20</v>
-      </c>
-      <c r="AE28" s="3">
-        <v>20</v>
-      </c>
-      <c r="AF28" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="3">
-        <v>26210</v>
-      </c>
-      <c r="AM28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="AO28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS28" s="3">
-        <v>50000</v>
-      </c>
-      <c r="AT28" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="AU28" s="3">
-        <v>2</v>
-      </c>
-      <c r="AV28" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="AW28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX28" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="AY28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC28" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD28" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE28" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BG28" s="3">
-        <v>13</v>
-      </c>
-      <c r="BH28" s="3">
-        <v>2</v>
-      </c>
-      <c r="BI28" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ28" s="2"/>
+      <c r="BI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ28" s="6"/>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
@@ -10237,377 +10278,377 @@
       </c>
       <c r="BJ47" s="2"/>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="5">
         <v>40</v>
       </c>
-      <c r="G48" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="G48" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5">
         <v>10</v>
       </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="J48" s="5">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
         <v>7</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="5">
         <v>40</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="5">
         <v>30</v>
       </c>
-      <c r="N48" s="3">
-        <v>20</v>
-      </c>
-      <c r="O48" s="2">
+      <c r="N48" s="5">
+        <v>20</v>
+      </c>
+      <c r="O48" s="6">
         <v>0.5</v>
       </c>
-      <c r="P48" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="P48" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="5">
         <v>330</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="5">
         <v>2000</v>
       </c>
-      <c r="S48" s="2">
+      <c r="S48" s="6">
         <v>200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="5">
         <v>10622</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="5">
         <v>11802</v>
       </c>
-      <c r="V48" s="2">
+      <c r="V48" s="6">
         <v>30</v>
       </c>
-      <c r="W48" s="2">
+      <c r="W48" s="6">
         <v>50</v>
       </c>
-      <c r="X48" s="2">
+      <c r="X48" s="6">
         <v>99</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="5">
         <v>1503</v>
       </c>
-      <c r="Z48" s="2">
+      <c r="Z48" s="6">
         <v>0.5</v>
       </c>
-      <c r="AA48" s="2">
+      <c r="AA48" s="6">
         <v>0.16680499911308289</v>
       </c>
-      <c r="AB48" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>20</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>20</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>20</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AB48" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AC48" s="5">
+        <v>20</v>
+      </c>
+      <c r="AD48" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE48" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF48" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="5">
         <v>22570</v>
       </c>
-      <c r="AM48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN48" s="3">
+      <c r="AM48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN48" s="5">
+        <v>1363637</v>
+      </c>
+      <c r="AO48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS48" s="5">
+        <v>2500</v>
+      </c>
+      <c r="AT48" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AU48" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV48" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AW48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX48" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="AY48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA48" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB48" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC48" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD48" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF48" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="BG48" s="5">
+        <v>16</v>
+      </c>
+      <c r="BH48" s="5">
+        <v>2</v>
+      </c>
+      <c r="BI48" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ48" s="6"/>
+    </row>
+    <row r="49" spans="1:62" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F49" s="5">
+        <v>45</v>
+      </c>
+      <c r="G49" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5">
+        <v>10</v>
+      </c>
+      <c r="J49" s="5">
+        <v>0</v>
+      </c>
+      <c r="K49" s="5">
+        <v>7</v>
+      </c>
+      <c r="L49" s="5">
+        <v>45</v>
+      </c>
+      <c r="M49" s="5">
+        <v>30</v>
+      </c>
+      <c r="N49" s="5">
+        <v>20</v>
+      </c>
+      <c r="O49" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="P49" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>330</v>
+      </c>
+      <c r="R49" s="5">
+        <v>1500</v>
+      </c>
+      <c r="S49" s="6">
+        <v>250</v>
+      </c>
+      <c r="T49" s="5">
+        <v>26655</v>
+      </c>
+      <c r="U49" s="5">
+        <v>29616</v>
+      </c>
+      <c r="V49" s="6">
+        <v>30</v>
+      </c>
+      <c r="W49" s="6">
+        <v>50</v>
+      </c>
+      <c r="X49" s="6">
+        <v>99</v>
+      </c>
+      <c r="Y49" s="5">
+        <v>3110</v>
+      </c>
+      <c r="Z49" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA49" s="6">
+        <v>0.11476700007915497</v>
+      </c>
+      <c r="AB49" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AC49" s="5">
+        <v>20</v>
+      </c>
+      <c r="AD49" s="5">
+        <v>20</v>
+      </c>
+      <c r="AE49" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF49" s="5">
+        <v>20</v>
+      </c>
+      <c r="AG49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="5">
+        <v>26210</v>
+      </c>
+      <c r="AM49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="5">
+        <v>2272728</v>
+      </c>
+      <c r="AO49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS49" s="5">
         <v>50000</v>
       </c>
-      <c r="AO48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS48" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AT48" s="3" t="s">
+      <c r="AT49" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="AU48" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV48" s="3" t="s">
+      <c r="AU49" s="5">
+        <v>2</v>
+      </c>
+      <c r="AV49" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AW48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX48" s="3" t="s">
+      <c r="AW49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX49" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="AY48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ48" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA48" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB48" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC48" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD48" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE48" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF48" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="BG48" s="3">
+      <c r="AY49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ49" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA49" s="5">
+        <v>1</v>
+      </c>
+      <c r="BB49" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC49" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD49" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF49" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="BG49" s="5">
         <v>16</v>
       </c>
-      <c r="BH48" s="3">
+      <c r="BH49" s="5">
         <v>2</v>
       </c>
-      <c r="BI48" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ48" s="2"/>
-    </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F49" s="3">
-        <v>45</v>
-      </c>
-      <c r="G49" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>10</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
-        <v>7</v>
-      </c>
-      <c r="L49" s="3">
-        <v>45</v>
-      </c>
-      <c r="M49" s="3">
-        <v>30</v>
-      </c>
-      <c r="N49" s="3">
-        <v>20</v>
-      </c>
-      <c r="O49" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="P49" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>330</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S49" s="2">
-        <v>250</v>
-      </c>
-      <c r="T49" s="3">
-        <v>26655</v>
-      </c>
-      <c r="U49" s="3">
-        <v>29616</v>
-      </c>
-      <c r="V49" s="2">
-        <v>30</v>
-      </c>
-      <c r="W49" s="2">
-        <v>50</v>
-      </c>
-      <c r="X49" s="2">
-        <v>99</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>3110</v>
-      </c>
-      <c r="Z49" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AA49" s="2">
-        <v>0.11476700007915497</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>-1</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>20</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>20</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>20</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>26210</v>
-      </c>
-      <c r="AM49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN49" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="AO49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS49" s="3">
-        <v>50000</v>
-      </c>
-      <c r="AT49" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="AU49" s="3">
-        <v>2</v>
-      </c>
-      <c r="AV49" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="AW49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX49" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="AY49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ49" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA49" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB49" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC49" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BE49" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF49" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BG49" s="3">
-        <v>16</v>
-      </c>
-      <c r="BH49" s="3">
-        <v>2</v>
-      </c>
-      <c r="BI49" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ49" s="2"/>
+      <c r="BI49" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ49" s="6"/>
     </row>
     <row r="50" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
@@ -14639,7 +14680,7 @@
       </c>
       <c r="I6">
         <f>GuardTowerItem!AN6</f>
-        <v>50000</v>
+        <v>1363637</v>
       </c>
       <c r="J6">
         <f>GuardTowerItem!AO6</f>
@@ -14849,7 +14890,7 @@
       </c>
       <c r="I7">
         <f>GuardTowerItem!AN7</f>
-        <v>1000000</v>
+        <v>2272728</v>
       </c>
       <c r="J7">
         <f>GuardTowerItem!AO7</f>
@@ -19049,7 +19090,7 @@
       </c>
       <c r="I27">
         <f>GuardTowerItem!AN27</f>
-        <v>50000</v>
+        <v>1363637</v>
       </c>
       <c r="J27">
         <f>GuardTowerItem!AO27</f>
@@ -19259,7 +19300,7 @@
       </c>
       <c r="I28">
         <f>GuardTowerItem!AN28</f>
-        <v>1000000</v>
+        <v>2272728</v>
       </c>
       <c r="J28">
         <f>GuardTowerItem!AO28</f>
@@ -23459,7 +23500,7 @@
       </c>
       <c r="I48">
         <f>GuardTowerItem!AN48</f>
-        <v>50000</v>
+        <v>1363637</v>
       </c>
       <c r="J48">
         <f>GuardTowerItem!AO48</f>
@@ -23669,7 +23710,7 @@
       </c>
       <c r="I49">
         <f>GuardTowerItem!AN49</f>
-        <v>1000000</v>
+        <v>2272728</v>
       </c>
       <c r="J49">
         <f>GuardTowerItem!AO49</f>

--- a/gu_in/Item.edf/25_GuardTowerItem/GuardTowerItem.xlsx
+++ b/gu_in/Item.edf/25_GuardTowerItem/GuardTowerItem.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D54D6-AE0C-4B9D-B6AC-EDF79086EA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47E5AFD-C966-41A6-90F2-C5428EA451AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GuardTowerItem" sheetId="1" r:id="rId1"/>
@@ -1154,9 +1154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1194,9 +1194,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1229,26 +1229,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1281,26 +1264,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2711,10 +2677,10 @@
         <v>250</v>
       </c>
       <c r="T7" s="5">
-        <v>26655</v>
+        <v>29655</v>
       </c>
       <c r="U7" s="5">
-        <v>29616</v>
+        <v>35616</v>
       </c>
       <c r="V7" s="6">
         <v>30</v>
@@ -2792,7 +2758,7 @@
         <v>289</v>
       </c>
       <c r="AU7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV7" s="5" t="s">
         <v>221</v>
@@ -6617,10 +6583,10 @@
         <v>250</v>
       </c>
       <c r="T28" s="5">
-        <v>26655</v>
+        <v>29655</v>
       </c>
       <c r="U28" s="5">
-        <v>29616</v>
+        <v>35616</v>
       </c>
       <c r="V28" s="6">
         <v>30</v>
@@ -6698,7 +6664,7 @@
         <v>289</v>
       </c>
       <c r="AU28" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV28" s="5" t="s">
         <v>221</v>
@@ -10523,10 +10489,10 @@
         <v>250</v>
       </c>
       <c r="T49" s="5">
-        <v>26655</v>
+        <v>29655</v>
       </c>
       <c r="U49" s="5">
-        <v>29616</v>
+        <v>35616</v>
       </c>
       <c r="V49" s="6">
         <v>30</v>
@@ -10604,7 +10570,7 @@
         <v>289</v>
       </c>
       <c r="AU49" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV49" s="5" t="s">
         <v>221</v>
@@ -14990,11 +14956,11 @@
       </c>
       <c r="AJ7">
         <f>GuardTowerItem!T7</f>
-        <v>26655</v>
+        <v>29655</v>
       </c>
       <c r="AK7">
         <f>GuardTowerItem!U7</f>
-        <v>29616</v>
+        <v>35616</v>
       </c>
       <c r="AL7">
         <f>GuardTowerItem!J7</f>
@@ -15037,7 +15003,7 @@
       </c>
       <c r="AV7">
         <f>GuardTowerItem!AU7</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="str">
         <f>GuardTowerItem!AV7</f>
@@ -19400,11 +19366,11 @@
       </c>
       <c r="AJ28">
         <f>GuardTowerItem!T28</f>
-        <v>26655</v>
+        <v>29655</v>
       </c>
       <c r="AK28">
         <f>GuardTowerItem!U28</f>
-        <v>29616</v>
+        <v>35616</v>
       </c>
       <c r="AL28">
         <f>GuardTowerItem!J28</f>
@@ -19447,7 +19413,7 @@
       </c>
       <c r="AV28">
         <f>GuardTowerItem!AU28</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" t="str">
         <f>GuardTowerItem!AV28</f>
@@ -23810,11 +23776,11 @@
       </c>
       <c r="AJ49">
         <f>GuardTowerItem!T49</f>
-        <v>26655</v>
+        <v>29655</v>
       </c>
       <c r="AK49">
         <f>GuardTowerItem!U49</f>
-        <v>29616</v>
+        <v>35616</v>
       </c>
       <c r="AL49">
         <f>GuardTowerItem!J49</f>
@@ -23857,7 +23823,7 @@
       </c>
       <c r="AV49">
         <f>GuardTowerItem!AU49</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW49" t="str">
         <f>GuardTowerItem!AV49</f>
